--- a/テスト仕様書_GIP_3.1.0.0→3.2.0.0.xlsx
+++ b/テスト仕様書_GIP_3.1.0.0→3.2.0.0.xlsx
@@ -5,24 +5,40 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Debugger\Downloads\260624_社内_GIP_試験テンプレート_ソース差分で影響度をAI判定_★260624更新\260625_GIP_3.1.0.0→3.2.0.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\260625_GIP_テスト仕様書_3.1.0.0→3.2.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9241B0A-E834-4299-9436-65A88DF48A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F30570-6EA4-4D64-8867-A34D8784EBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="影響度" sheetId="1" r:id="rId1"/>
     <sheet name="確認チェックリスト" sheetId="2" r:id="rId2"/>
     <sheet name="実施順序" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">確認チェックリスト!$A$1:$Q$51</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="374">
   <si>
     <t>3.1.0.0 → 3.2.0.0 影響度整理</t>
   </si>
@@ -249,9 +265,6 @@
     <t>NG時に疑う箇所</t>
   </si>
   <si>
-    <t>結果/メモ</t>
-  </si>
-  <si>
     <t>起動/旧ワーク</t>
   </si>
   <si>
@@ -1054,13 +1067,268 @@
   </si>
   <si>
     <t>46-48</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>1回目</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2回目</t>
+    <rPh sb="1" eb="3">
+      <t>カイメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保留</t>
+  </si>
+  <si>
+    <t>ゲージ画面は未使用、基準画像には中心線表示しない仕様。</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ミシヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>キジュンガゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>チュウシンセン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グループ判定の追加、初回実行フラグの配列化</t>
+    <rPh sb="4" eb="6">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テンプレートのエクセルが未対応。社内向け機能なのでOKとする。</t>
+    <rPh sb="12" eb="15">
+      <t>ミタイオウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シャナイム</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PTNエラー時に信号でなかった。カメラ56の分岐漏れ。</t>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Load_FilterSettingsにデグレあり。良かれと思ったコード整理の結果。</t>
+    <rPh sb="26" eb="27">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3つ位置合わせを作成し、2つ目を削除　→　空間座標の修正漏れあり。</t>
+    <rPh sb="2" eb="5">
+      <t>イチア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>クウカンザヒョウ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>シュウセイモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他Verへの影響</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>エイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.xx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.xx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.xx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.xx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5.xx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>住友</t>
+    <rPh sb="0" eb="2">
+      <t>スミトモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢崎</t>
+    <rPh sb="0" eb="2">
+      <t>ヤザキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市村</t>
+    <rPh sb="0" eb="2">
+      <t>イチムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｲﾘｿ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IPEX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運用で使わないのでOKとする。</t>
+    <rPh sb="0" eb="2">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>机上確認不可</t>
+    <rPh sb="0" eb="2">
+      <t>キジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>机上</t>
+  </si>
+  <si>
+    <t>試験区分</t>
+    <rPh sb="0" eb="4">
+      <t>シケンクブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>試験結果</t>
+    <rPh sb="0" eb="2">
+      <t>シケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>試験結果(1回目)のNG理由</t>
+    <rPh sb="0" eb="2">
+      <t>シケン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>リユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ56の初期値がONだったので OFFに修正。</t>
+    <rPh sb="6" eb="9">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1087,8 +1355,30 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1105,8 +1395,44 @@
         <fgColor rgb="FF5B9BD5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1144,13 +1470,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1196,7 +1612,67 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1762,1214 +2238,1990 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q51"/>
+  <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="66.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="79.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="63.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="2.625" style="1"/>
+    <col min="1" max="1" width="3.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.25" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.25" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="6.125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="54.125" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="5.625" style="25" customWidth="1"/>
+    <col min="18" max="16384" width="2.625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="J1" s="31"/>
+      <c r="K1" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="P2" s="26" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="P3" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q3" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A4" s="19">
+        <v>1</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="D4" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A5" s="19">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="C5" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="D5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A6" s="19">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="C6" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="D6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J6" s="23"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A7" s="19">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A8" s="19">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C8" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J8" s="23"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A9" s="19">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A10" s="19">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J10" s="23"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A11" s="19">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A12" s="19">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="C12" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A13" s="19">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="D13" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J13" s="23"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A14" s="19">
+        <v>11</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J14" s="23"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A15" s="19">
+        <v>12</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J15" s="23"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A16" s="19">
+        <v>13</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="C16" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J16" s="23"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A17" s="19">
+        <v>14</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C17" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J17" s="23"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A18" s="19">
+        <v>15</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J18" s="23"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A19" s="19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J19" s="23"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A20" s="19">
+        <v>17</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="C20" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J20" s="23"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A21" s="19">
         <v>18</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="B21" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="C21" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J21" s="23"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A22" s="19">
+        <v>19</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="C22" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J22" s="23"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A23" s="19">
+        <v>20</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="C23" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J23" s="23"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A24" s="19">
+        <v>21</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="C24" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J24" s="23"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A25" s="19">
+        <v>22</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A26" s="19">
+        <v>23</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J26" s="23"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A27" s="19">
+        <v>24</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="J27" s="23"/>
+      <c r="K27" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A28" s="19">
+        <v>25</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="C28" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J28" s="23"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A29" s="19">
+        <v>26</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="C29" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J29" s="23"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A30" s="19">
+        <v>27</v>
+      </c>
+      <c r="B30" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="C30" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A31" s="19">
+        <v>28</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="C31" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J31" s="23"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A32" s="19">
+        <v>29</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="J32" s="23"/>
+      <c r="K32" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A33" s="19">
+        <v>30</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J33" s="23"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A34" s="19">
+        <v>31</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="H34" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="J34" s="23"/>
+      <c r="K34" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A35" s="19">
+        <v>32</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="J35" s="23"/>
+      <c r="K35" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A36" s="19">
+        <v>33</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+      <c r="C36" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="H36" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J36" s="23"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A37" s="19">
+        <v>34</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C37" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="N37" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="O37" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="P37" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q37" s="20" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A38" s="19">
+        <v>35</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="C38" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J38" s="23"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A39" s="19">
+        <v>36</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="H39" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I39" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J39" s="23"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A40" s="19">
+        <v>37</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="H40" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J40" s="23"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A41" s="19">
+        <v>38</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="H41" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="J41" s="23"/>
+      <c r="K41" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A42" s="19">
+        <v>39</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I42" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J42" s="23"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A43" s="19">
+        <v>40</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J43" s="23"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A44" s="19">
+        <v>41</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I44" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J44" s="23"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A45" s="19">
+        <v>42</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="H45" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J45" s="23"/>
+      <c r="K45" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A46" s="19">
+        <v>43</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J46" s="23"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A47" s="19">
+        <v>44</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="H47" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I47" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J47" s="23"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A48" s="19">
+        <v>45</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I48" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J48" s="23"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A49" s="19">
+        <v>46</v>
+      </c>
+      <c r="B49" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="C49" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="H49" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I49" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="J49" s="23"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A50" s="19">
+        <v>47</v>
+      </c>
+      <c r="B50" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="15"/>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A27" s="4">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="C50" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="H50" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A51" s="19">
+        <v>48</v>
+      </c>
+      <c r="B51" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H29" s="15"/>
-    </row>
-    <row r="30" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H30" s="15"/>
-    </row>
-    <row r="31" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A31" s="4">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H31" s="15"/>
-    </row>
-    <row r="32" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
-        <v>31</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H32" s="15"/>
-    </row>
-    <row r="33" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
-        <v>32</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="H33" s="15"/>
-    </row>
-    <row r="34" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A34" s="4">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="H34" s="15"/>
-    </row>
-    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A36" s="4">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="H36" s="15"/>
-    </row>
-    <row r="37" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="H37" s="15"/>
-    </row>
-    <row r="38" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A38" s="4">
-        <v>37</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H38" s="15"/>
-    </row>
-    <row r="39" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A39" s="4">
-        <v>38</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="H39" s="15"/>
-    </row>
-    <row r="40" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A40" s="4">
-        <v>39</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H40" s="15"/>
-    </row>
-    <row r="41" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A41" s="4">
-        <v>40</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="H41" s="15"/>
-    </row>
-    <row r="42" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A42" s="4">
-        <v>41</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="H42" s="15"/>
-    </row>
-    <row r="43" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A43" s="4">
-        <v>42</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H43" s="15"/>
-    </row>
-    <row r="44" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A44" s="4">
-        <v>43</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="H44" s="15"/>
-    </row>
-    <row r="45" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A45" s="4">
-        <v>44</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="H45" s="15"/>
-    </row>
-    <row r="46" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A46" s="4">
-        <v>45</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="H46" s="15"/>
-    </row>
-    <row r="47" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A47" s="15">
-        <v>46</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="H47" s="15"/>
-    </row>
-    <row r="48" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A48" s="15">
-        <v>47</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="G48" s="15" t="s">
+      <c r="C51" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H48" s="15"/>
-    </row>
-    <row r="49" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A49" s="15">
-        <v>48</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="15" t="s">
+      <c r="D51" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="E51" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="F51" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="G51" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="G49" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="H49" s="15"/>
+      <c r="H51" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="J51" s="23"/>
+      <c r="K51" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="G1:G3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B2:B49">
+  <conditionalFormatting sqref="B4:B51">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>B2="S"</formula>
+      <formula>B4="S"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>B2="A"</formula>
+      <formula>B4="A"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>B2="B"</formula>
+      <formula>B4="B"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="H2:H46" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="I4:J51" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"未実施,OK,NG,保留"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H4:H51" xr:uid="{699F37C1-158E-4DCC-B433-A2397436A720}">
+      <formula1>"机上,実機"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2996,22 +4248,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>297</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -3019,19 +4271,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -3039,19 +4291,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -3059,19 +4311,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -3079,19 +4331,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
@@ -3099,19 +4351,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -3119,19 +4371,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
@@ -3139,19 +4391,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
@@ -3159,19 +4411,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
@@ -3179,19 +4431,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>343</v>
       </c>
     </row>
   </sheetData>
